--- a/output/pdf_financials_xlsx/REAL.xlsx
+++ b/output/pdf_financials_xlsx/REAL.xlsx
@@ -819,34 +819,34 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.139</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.698</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.986</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.611</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.151</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.134</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.825</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-1.779</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-1.721</v>
       </c>
     </row>
     <row r="13">
@@ -1474,34 +1474,34 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.079</v>
+        <v>-6.059</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-55.941</v>
+        <v>-55.802</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.429</v>
+        <v>-6.731</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>24.398</v>
+        <v>25.384</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>104.262</v>
+        <v>104.873</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>79.19799999999999</v>
+        <v>79.349</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-9.265000000000001</v>
+        <v>-9.131</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-6.196</v>
+        <v>-5.371</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.782</v>
+        <v>0.997</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-27.676</v>
+        <v>-25.955</v>
       </c>
     </row>
     <row r="28">
@@ -1548,34 +1548,34 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.76</v>
+        <v>6.78</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-36.292</v>
+        <v>-36.153</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>10.807</v>
+        <v>11.505</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>33.379</v>
+        <v>34.365</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>105.989</v>
+        <v>106.6</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>80.89700000000001</v>
+        <v>81.048</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-7.876</v>
+        <v>-7.742</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.711</v>
+        <v>-3.886</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.89</v>
+        <v>2.669</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-25.854</v>
+        <v>-24.133</v>
       </c>
     </row>
     <row r="30">
@@ -1585,34 +1585,34 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2.719807521313876</v>
+        <v>2.727854289128414</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-11.97850654837347</v>
+        <v>-11.9326283269962</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3.839744751306621</v>
+        <v>4.087745291365104</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>10.34889020484472</v>
+        <v>10.65459156623891</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>23.24600554891489</v>
+        <v>23.38001294015725</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>16.0475851356954</v>
+        <v>16.07753909388284</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-2.318912266445257</v>
+        <v>-2.279458959728184</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-2.874068108886367</v>
+        <v>-2.370755396122357</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.5152788874607751</v>
+        <v>1.545257697340235</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-15.23072300867752</v>
+        <v>-14.21687314800087</v>
       </c>
     </row>
     <row r="31">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -22394,7 +22394,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -23588,7 +23588,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -23656,7 +23656,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -25078,7 +25078,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -27270,7 +27270,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -27338,7 +27338,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E343" s="5" t="n">
@@ -28882,7 +28882,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -28948,7 +28948,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -31048,7 +31048,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E400" s="5" t="n">

--- a/output/pdf_financials_xlsx/REAL.xlsx
+++ b/output/pdf_financials_xlsx/REAL.xlsx
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.603</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -5115,28 +5115,28 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-0.404</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-0.366</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-0.754</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-0.471</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-1.571</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-0.145</v>
       </c>
       <c r="H126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>-0.139</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>0</v>
@@ -12752,7 +12752,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E117" s="5" t="n">
         <v>-0.404</v>
       </c>
@@ -13452,7 +13456,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -14484,7 +14492,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -15122,7 +15134,11 @@
           <t>Loss on disposal of property and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -18684,7 +18700,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/REAL.xlsx
+++ b/output/pdf_financials_xlsx/REAL.xlsx
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-6.079</v>
+        <v>-13.049</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-55.941</v>
@@ -985,10 +985,10 @@
         <v>79.19799999999999</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-9.265000000000001</v>
+        <v>-21.614</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-6.196</v>
+        <v>-15.341</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-0.782</v>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>6.97</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>32.172</v>
@@ -1022,10 +1022,10 @@
         <v>-46.118</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>12.349</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>9.145</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>0.8</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.059</v>
+        <v>-13.029</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-55.802</v>
@@ -1492,10 +1492,10 @@
         <v>79.349</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-9.131</v>
+        <v>-21.48</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.371</v>
+        <v>-14.516</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>0.997</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.78</v>
+        <v>-0.19</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-36.153</v>
@@ -1566,10 +1566,10 @@
         <v>81.048</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-7.742</v>
+        <v>-20.091</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.886</v>
+        <v>-13.031</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.669</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2.727854289128414</v>
+        <v>-0.0764442942381119</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-11.9326283269962</v>
@@ -1603,10 +1603,10 @@
         <v>16.07753909388284</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-2.279458959728184</v>
+        <v>-5.915346158602293</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-2.370755396122357</v>
+        <v>-7.949900557609478</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>1.545257697340235</v>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-53.41405471683653</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-57.51059151606156</v>
@@ -1640,10 +1640,10 @@
         <v>58.23126846637542</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-57.134264828352</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-59.61149859852682</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-102.3017902813299</v>
@@ -5250,10 +5250,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C129" s="3" t="n">
+        <v>54.698</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>-12.114</v>
@@ -5273,10 +5271,8 @@
       <c r="I129" s="3" t="n">
         <v>-0.445</v>
       </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J129" s="3" t="n">
+        <v>1.522</v>
       </c>
       <c r="K129" s="1" t="inlineStr">
         <is>
@@ -5480,33 +5476,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C135" s="3" t="n">
+        <v>-10.33</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>8.115</v>
+        <v>9.949</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>22.463</v>
+        <v>23.578</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>72.673</v>
+        <v>72.861</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>24.96</v>
+        <v>21.996</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>16.418</v>
+        <v>16.552</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-2.557</v>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.564</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>5.449</v>
       </c>
       <c r="K135" s="1" t="inlineStr">
         <is>
@@ -12106,7 +12098,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -12556,7 +12552,11 @@
           <t>Cash generated from (utilized in) operating activities</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -15400,7 +15400,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -16828,7 +16832,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -18002,7 +18010,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -19680,7 +19692,11 @@
           <t>Cash generated from (utilized in) operating activities</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -23870,7 +23886,11 @@
           <t>LOSS BEFORE INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -24052,7 +24072,11 @@
           <t>TOTAL INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -26262,7 +26286,11 @@
           <t>(LOSS) INCOME BEFORE INCOME TAX (RECOVERY) EXPENSE</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -26326,7 +26354,11 @@
           <t>TOTAL INCOME TAX (RECOVERY) EXPENSE</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -31328,7 +31360,11 @@
           <t>LOSS BEFORE INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E404" s="5" t="n">
         <v>-6.97</v>
       </c>
@@ -31392,7 +31428,11 @@
           <t>TOTAL INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E405" s="5" t="n">
         <v>-0.891</v>
       </c>
